--- a/Resultado_Busca2.xlsx
+++ b/Resultado_Busca2.xlsx
@@ -425,162 +425,78 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Programa</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Book</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Programa</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>CS00000F</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>CSC00900</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>CS00000F</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CSC00900</t>
+          <t>CS00000M</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CS00000M</t>
+          <t>CSC00900, CSC00903, CSF00100</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CSC00900</t>
+          <t>CS00000S</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CS00000S</t>
+          <t>CS00000M, CSC00900, CSC00903</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CSC00900</t>
+          <t>CS00001M</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CS00001M</t>
+          <t>CSC00900, CSC00903, CSF00100</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CSC00903</t>
+          <t>Nenhuma referência encontrada</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CS00000M</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CSC00903</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>CS00000S</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CSC00903</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>CS00001M</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CSF00000</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Nenhuma referência encontrada</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CSF00100</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CS00000M</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CSF00100</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>CS00001M</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CSF00300</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Nenhuma referência encontrada</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CSF33300</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Nenhuma referência encontrada</t>
+          <t>CSF00000, CSF00300, CSF33300</t>
         </is>
       </c>
     </row>
